--- a/performance-dashboard/archive/交易表现_20260203.xlsx
+++ b/performance-dashboard/archive/交易表现_20260203.xlsx
@@ -531,26 +531,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,010,554.01</t>
+          <t>¥1,032,327.15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+10,554.01</t>
+          <t>¥+32,327.15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+3.23%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+8.62%</t>
+          <t>+27.50%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.438</v>
+        <v>1.264</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -559,24 +559,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0414%</t>
+          <t>0.1074%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19.2732%</t>
+          <t>19.8473%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -683,26 +683,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥999,897.23</t>
+          <t>¥1,013,995.87</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥-102.77</t>
+          <t>¥+13,995.87</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.40%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+11.20%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-0.076</v>
+        <v>0.697</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -711,24 +711,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0036%</t>
+          <t>0.0476%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14.0505%</t>
+          <t>14.3644%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -835,26 +835,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,003,463.46</t>
+          <t>¥1,015,237.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+3,463.46</t>
+          <t>¥+15,237.23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>+12.24%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.133</v>
+        <v>1.007</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -863,24 +863,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0132%</t>
+          <t>0.0494%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10.0520%</t>
+          <t>10.3997%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -911,26 +911,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>¥1,044,845.94</t>
+          <t>¥1,050,309.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>¥+44,845.94</t>
+          <t>¥+50,309.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+4.48%</t>
+          <t>+5.03%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+41.27%</t>
+          <t>+45.47%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3.967</v>
+        <v>4.351</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -939,24 +939,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.1431%</t>
+          <t>0.1550%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8.5895%</t>
+          <t>8.5191%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -987,26 +987,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>¥1,020,044.35</t>
+          <t>¥1,030,867.82</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>¥+20,044.35</t>
+          <t>¥+30,867.82</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.00%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+16.92%</t>
+          <t>+26.13%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.805</v>
+        <v>2.67</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1015,24 +1015,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.0653%</t>
+          <t>0.0964%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8.0199%</t>
+          <t>8.3590%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1063,26 +1063,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>¥1,004,929.36</t>
+          <t>¥1,023,654.23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>¥+4,929.36</t>
+          <t>¥+23,654.23</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+2.37%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+19.55%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.206</v>
+        <v>1.051</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1091,24 +1091,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.0214%</t>
+          <t>0.0789%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16.5132%</t>
+          <t>17.0308%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1215,26 +1215,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>¥1,002,361.69</t>
+          <t>¥1,014,715.29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>¥+2,361.69</t>
+          <t>¥+14,715.29</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.87%</t>
+          <t>+11.80%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.049</v>
+        <v>0.91</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1243,24 +1243,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.0100%</t>
+          <t>0.0482%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10.8078%</t>
+          <t>11.1606%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1291,26 +1291,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>¥992,161.83</t>
+          <t>¥1,010,898.93</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>¥-7,838.17</t>
+          <t>¥+10,898.93</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.01%</t>
+          <t>+8.63%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-0.441</v>
+        <v>0.478</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1319,24 +1319,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-0.0202%</t>
+          <t>0.0395%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16.0361%</t>
+          <t>16.6408%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1367,26 +1367,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>¥995,189.39</t>
+          <t>¥997,512.81</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>¥-4,810.61</t>
+          <t>¥-2,487.19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.97%</t>
+          <t>-2.00%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-0.191</v>
+        <v>-0.095</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1395,24 +1395,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-0.0079%</t>
+          <t>0.0002%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20.7391%</t>
+          <t>20.4021%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1443,26 +1443,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>¥1,001,757.22</t>
+          <t>¥1,012,531.22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>¥+1,757.22</t>
+          <t>¥+12,531.22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-0.005</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1471,24 +1471,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.0077%</t>
+          <t>0.0410%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>10.0141%</t>
+          <t>10.2882%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1519,26 +1519,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>¥996,835.60</t>
+          <t>¥1,000,956.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>¥-3,164.40</t>
+          <t>¥+956.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-1.234</v>
+        <v>-0.307</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1547,24 +1547,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-0.0100%</t>
+          <t>0.0033%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>3.6381%</t>
+          <t>3.7668%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1595,26 +1595,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>¥997,466.80</t>
+          <t>¥1,002,799.30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>¥-2,533.20</t>
+          <t>¥+2,799.30</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.98%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-0.821</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1623,24 +1623,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-0.0077%</t>
+          <t>0.0092%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4.7824%</t>
+          <t>4.9396%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1767,26 +1767,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,010,554.01</t>
+          <t>¥1,032,327.15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+10,554.01</t>
+          <t>¥+32,327.15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+3.23%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+8.62%</t>
+          <t>+27.50%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.438</v>
+        <v>1.264</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1795,24 +1795,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0414%</t>
+          <t>0.1074%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19.2732%</t>
+          <t>19.8473%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1919,26 +1919,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥999,897.23</t>
+          <t>¥1,013,995.87</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥-102.77</t>
+          <t>¥+13,995.87</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.40%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+11.20%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-0.076</v>
+        <v>0.697</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1947,24 +1947,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0036%</t>
+          <t>0.0476%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14.0505%</t>
+          <t>14.3644%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2071,26 +2071,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,003,463.46</t>
+          <t>¥1,015,237.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+3,463.46</t>
+          <t>¥+15,237.23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>+12.24%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.133</v>
+        <v>1.007</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2099,24 +2099,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0132%</t>
+          <t>0.0494%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10.0520%</t>
+          <t>10.3997%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2243,26 +2243,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,044,845.94</t>
+          <t>¥1,050,309.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+44,845.94</t>
+          <t>¥+50,309.94</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+4.48%</t>
+          <t>+5.03%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+41.27%</t>
+          <t>+45.47%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.967</v>
+        <v>4.351</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2271,24 +2271,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1431%</t>
+          <t>0.1550%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8.5895%</t>
+          <t>8.5191%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2319,26 +2319,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,020,044.35</t>
+          <t>¥1,030,867.82</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+20,044.35</t>
+          <t>¥+30,867.82</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.00%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+16.92%</t>
+          <t>+26.13%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.805</v>
+        <v>2.67</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2347,24 +2347,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0653%</t>
+          <t>0.0964%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8.0199%</t>
+          <t>8.3590%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2395,26 +2395,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,004,929.36</t>
+          <t>¥1,023,654.23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+4,929.36</t>
+          <t>¥+23,654.23</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+2.37%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+19.55%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.206</v>
+        <v>1.051</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2423,24 +2423,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0214%</t>
+          <t>0.0789%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16.5132%</t>
+          <t>17.0308%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2547,26 +2547,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,002,361.69</t>
+          <t>¥1,014,715.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+2,361.69</t>
+          <t>¥+14,715.29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.87%</t>
+          <t>+11.80%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.049</v>
+        <v>0.91</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2575,24 +2575,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0100%</t>
+          <t>0.0482%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10.8078%</t>
+          <t>11.1606%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2719,26 +2719,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥992,161.83</t>
+          <t>¥1,010,898.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥-7,838.17</t>
+          <t>¥+10,898.93</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.01%</t>
+          <t>+8.63%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-0.441</v>
+        <v>0.478</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2747,24 +2747,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.0202%</t>
+          <t>0.0395%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16.0361%</t>
+          <t>16.6408%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2795,26 +2795,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥995,189.39</t>
+          <t>¥997,512.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥-4,810.61</t>
+          <t>¥-2,487.19</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.97%</t>
+          <t>-2.00%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-0.191</v>
+        <v>-0.095</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2823,24 +2823,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-0.0079%</t>
+          <t>0.0002%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20.7391%</t>
+          <t>20.4021%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2871,26 +2871,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,001,757.22</t>
+          <t>¥1,012,531.22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+1,757.22</t>
+          <t>¥+12,531.22</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-0.005</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2899,24 +2899,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0077%</t>
+          <t>0.0410%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10.0141%</t>
+          <t>10.2882%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2947,26 +2947,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥996,835.60</t>
+          <t>¥1,000,956.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥-3,164.40</t>
+          <t>¥+956.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-1.234</v>
+        <v>-0.307</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2975,24 +2975,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.0100%</t>
+          <t>0.0033%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3.6381%</t>
+          <t>3.7668%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -3023,26 +3023,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥997,466.80</t>
+          <t>¥1,002,799.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥-2,533.20</t>
+          <t>¥+2,799.30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.98%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-0.821</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3051,24 +3051,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.0077%</t>
+          <t>0.0092%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>4.7824%</t>
+          <t>4.9396%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>

--- a/performance-dashboard/archive/交易表现_20260203.xlsx
+++ b/performance-dashboard/archive/交易表现_20260203.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模式1-纯数据" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模式2-数据+技术" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模式3-数据+新闻" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模式4-多智能体" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模式5-巴菲特" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,26 +609,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,031,521.13</t>
+          <t>¥1,049,011.17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+31,521.13</t>
+          <t>¥+49,011.17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+3.15%</t>
+          <t>+4.90%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+27.69%</t>
+          <t>+44.11%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.337</v>
+        <v>1.981</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,24 +637,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1072%</t>
+          <t>0.1569%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18.7317%</t>
+          <t>18.9515%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -661,7 +663,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -759,26 +761,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥997,597.22</t>
+          <t>¥1,013,117.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥-2,402.78</t>
+          <t>¥+13,117.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>+10.46%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-0.309</v>
+        <v>0.779</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -787,24 +789,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.0054%</t>
+          <t>0.0434%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10.8126%</t>
+          <t>11.4827%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -813,7 +815,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1139,26 +1141,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>¥1,041,871.47</t>
+          <t>¥1,068,188.97</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>¥+41,871.47</t>
+          <t>¥+68,188.97</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+4.19%</t>
+          <t>+6.82%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+38.13%</t>
+          <t>+65.49%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.476</v>
+        <v>2.232</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1167,24 +1169,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.1432%</t>
+          <t>0.2177%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>23.1144%</t>
+          <t>23.6832%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1193,7 +1195,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1648,6 +1650,462 @@
         </is>
       </c>
       <c r="P16" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>模式4-多智能体</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>multi-agent</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>¥1,040,969.99</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>¥+40,969.99</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>+4.10%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>+37.19%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2.433</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3.10%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>51.6%</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.1330%</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>12.9580%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>32</v>
+      </c>
+      <c r="N17" t="n">
+        <v>32</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>deepseek-v3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>¥1,163,418.90</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>¥+163,418.90</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>+16.34%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>+229.36%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>11.676</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>80.6%</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.4916%</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>10.4408%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>32</v>
+      </c>
+      <c r="N18" t="n">
+        <v>32</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>gemini-3-pro</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>¥1,191,654.11</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>¥+191,654.11</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>+19.17%</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>+297.82%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>12.188</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>90.3%</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0.5699%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>11.6204%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>32</v>
+      </c>
+      <c r="N19" t="n">
+        <v>32</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>gpt-5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>¥1,324,359.42</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>¥+324,359.42</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>+32.44%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>+813.68%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>18.525</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>90.3%</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0.9133%</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>12.3172%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>32</v>
+      </c>
+      <c r="N20" t="n">
+        <v>32</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>llama-3.1-405b</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>¥1,220,109.37</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>¥+220,109.37</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>+22.01%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>+379.06%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>9.349</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>83.9%</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0.6496%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>17.2990%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>32</v>
+      </c>
+      <c r="N21" t="n">
+        <v>32</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>qwen-72b</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>¥1,521,805.19</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>¥+521,805.19</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>+52.18%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>+2629.47%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>18.973</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>90.3%</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1.3701%</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>18.0926%</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>32</v>
+      </c>
+      <c r="N22" t="n">
+        <v>32</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>20260203</t>
         </is>
@@ -1843,26 +2301,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,031,521.13</t>
+          <t>¥1,049,011.17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+31,521.13</t>
+          <t>¥+49,011.17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+3.15%</t>
+          <t>+4.90%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+27.69%</t>
+          <t>+44.11%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.337</v>
+        <v>1.981</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1871,24 +2329,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1072%</t>
+          <t>0.1569%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18.7317%</t>
+          <t>18.9515%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -1897,7 +2355,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1995,26 +2453,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥997,597.22</t>
+          <t>¥1,013,117.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥-2,402.78</t>
+          <t>¥+13,117.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>+10.46%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-0.309</v>
+        <v>0.779</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2023,24 +2481,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.0054%</t>
+          <t>0.0434%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10.8126%</t>
+          <t>11.4827%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2049,7 +2507,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2471,26 +2929,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,041,871.47</t>
+          <t>¥1,068,188.97</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+41,871.47</t>
+          <t>¥+68,188.97</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+4.19%</t>
+          <t>+6.82%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+38.13%</t>
+          <t>+65.49%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.476</v>
+        <v>2.232</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2499,24 +2957,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.1432%</t>
+          <t>0.2177%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23.1144%</t>
+          <t>23.6832%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2525,7 +2983,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -3084,4 +3542,652 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>模式</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>初始资金</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>最新资金</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>总利润</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>总收益率(%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>年化收益率(%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>夏普比率</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>最大回撤(%)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>胜率(%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>日均收益率(%)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>年化波动率(%)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>交易日数</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>文件数量</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>分析日期</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>数据日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>模式4-多智能体</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>multi-agent</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>¥1,040,969.99</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>¥+40,969.99</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>+4.10%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>+37.19%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2.433</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3.10%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>51.6%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.1330%</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>12.9580%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>模式</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>初始资金</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>最新资金</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>总利润</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>总收益率(%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>年化收益率(%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>夏普比率</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>最大回撤(%)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>胜率(%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>日均收益率(%)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>年化波动率(%)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>交易日数</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>文件数量</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>分析日期</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>数据日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>deepseek-v3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>¥1,163,418.90</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>¥+163,418.90</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>+16.34%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>+229.36%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>11.676</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>80.6%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.4916%</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10.4408%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>gemini-3-pro</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>¥1,191,654.11</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>¥+191,654.11</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>+19.17%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>+297.82%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>12.188</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>90.3%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.5699%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>11.6204%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>32</v>
+      </c>
+      <c r="N3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>gpt-5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>¥1,324,359.42</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>¥+324,359.42</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>+32.44%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>+813.68%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>18.525</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>90.3%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.9133%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>12.3172%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>32</v>
+      </c>
+      <c r="N4" t="n">
+        <v>32</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>llama-3.1-405b</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>¥1,220,109.37</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>¥+220,109.37</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>+22.01%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>+379.06%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>9.349</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>83.9%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.6496%</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>17.2990%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>32</v>
+      </c>
+      <c r="N5" t="n">
+        <v>32</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>qwen-72b</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>¥1,521,805.19</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>¥+521,805.19</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>+52.18%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>+2629.47%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>18.973</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>90.3%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1.3701%</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>18.0926%</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>32</v>
+      </c>
+      <c r="N6" t="n">
+        <v>32</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>